--- a/光伏配储项目/电价数据/2026/加林站.xlsx
+++ b/光伏配储项目/电价数据/2026/加林站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5535599999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.50918</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8490800000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12248</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01118</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.90535</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.70168</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.71147</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5312899999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58341</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.51688</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.67252</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.67265</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.66274</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.69072</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.6808</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.64289</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.66899</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.5182899999999999</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.68367</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.5389700000000001</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.68169</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.6896</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.5427799999999999</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.7146399999999999</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.80432</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85589</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67528</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6705</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73199</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75466</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00697</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.9910800000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08194</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7496499999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.69604</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50056</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78284</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.94711</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.30962</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52244</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76576</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74602</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.92555</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04569</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31225</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.11687</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.11264</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73298</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.20686</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16689</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22656</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53359</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.09765</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.2446</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.4744</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.3024</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23422</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79673</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.40831</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35206</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28262</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8022400000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42188</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16626</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17595</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.60685</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.50693</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58116</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.5124500000000001</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.5055500000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.75662</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.05917</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83257</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.58448</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.47816</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50368</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.93296</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.14891</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11884</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03581</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98409</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70627</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54728</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5659299999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67815</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15029</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.22836</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47196</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15531</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62604</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07736</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.24899</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13333</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28208</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6212799999999999</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63724</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56964</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62149</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.15711</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16571</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17444</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.16909</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18786</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20266</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19394</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66833</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.15871</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2054</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20644</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50262</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.40691</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16505</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50968</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.2638</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74213</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76489</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91543</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.59766</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6751200000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.68651</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5285700000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57138</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5027200000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8137300000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.58387</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5759099999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.62326</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.47789</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.57121</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48227</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.56935</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.51932</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.49982</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.45481</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69162</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10696</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87313</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74309</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70225</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60402</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64301</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72785</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16275</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.51877</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6754600000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16478</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.61717</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16245</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79153</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9369299999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16113</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16265</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89093</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47444</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67379</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16366</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02649</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.1618</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.38911</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23221</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16324</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21507</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20904</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.39772</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26697</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28406</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64681</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.16809</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17121</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.77897</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03666</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07647</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09733</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20188</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16609</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24573</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.99273</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7530800000000001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.70957</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5295299999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10557</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7141000000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7078300000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.15927</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6727300000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8471000000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.53383</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.55565</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.17244</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5825900000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.64373</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5090899999999999</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.5007200000000001</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.51409</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.56649</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.48663</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.48771</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45314</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48745</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6755099999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7177899999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9319400000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16558</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30673</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.83608</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.54912</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.6653</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90286</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86233</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16196</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43912</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77208</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.95057</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20156</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6875599999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12268</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52177</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6530199999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99383</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10065</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24773</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16607</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.05811</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.9791799999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02495</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.24835</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.43831</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79144</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34597</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18791</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84616</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07158</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.15887</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12055</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15127</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25229</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31596</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15131</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26717</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18645</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18557</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18637</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18619</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17169</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.14929</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72242</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72453</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32159</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74312</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49311</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50401</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52239</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45473</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71546</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8466</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61395</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7006699999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7256900000000001</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84415</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70416</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.54996</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53774</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59151</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08403000000000001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5494199999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48142</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51127</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48238</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48251</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59317</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50481</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50532</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48556</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.18878</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96361</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58958</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.53635</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52178</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.53516</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.50313</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.66926</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.51811</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.50142</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07324</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04525</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08273</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04669</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.58545</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.52988</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.55245</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5317499999999999</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.53095</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33431</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.54946</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26939</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.73988</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.87226</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67318</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6471399999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.66611</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74703</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9372699999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7286699999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73026</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88593</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53485</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08477999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73056</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7265199999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6375299999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60205</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7884800000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78206</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.59957</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74074</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01706</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.4042</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8417</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43184</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29388</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.78687</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.37864</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04343</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.7983</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.39891</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76356</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44228</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77338</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8003400000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7876799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50193</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41133</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21844</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6094299999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.55602</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.5649</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.57172</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5732999999999999</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.55235</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.48691</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.53313</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.5042300000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.50812</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.50462</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.54128</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.55933</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.55991</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.48694</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56359</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6661699999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07981</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63786</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50215</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5686599999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59883</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00078</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33872</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30628</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27491</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8018500000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57272</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65042</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.54999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95384</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77574</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72487</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6414099999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57474</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9864700000000001</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.92245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78299</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54011</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.66755</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58336</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.66562</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.61913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.65959</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.6965800000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.63618</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.6582100000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58114</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5767100000000001</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65611</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67177</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.6161799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.66531</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68432</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.75946</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.6747300000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75567</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68333</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6671699999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.65652</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6127999999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.65563</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.59714</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5341699999999999</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60009</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.54732</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5729099999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.53372</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.52306</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46177</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.56947</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5970299999999999</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6126200000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.67074</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.52615</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5403300000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.49323</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5168400000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.48694</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6399900000000001</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51154</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61673</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72599</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.86915</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.10846</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9314</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5438500000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11241</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84177</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94726</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85726</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63862</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80783</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06515</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.56272</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8728400000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.9860800000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5227999999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18718</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7819299999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81145</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7326900000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7381599999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.1958</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.5122</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7923600000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7474400000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16417</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9203600000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64198</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.65869</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.6996100000000001</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55316</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16298</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61062</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9082100000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5751000000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.56496</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.32779</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.25239</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22019</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.31972</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.99951</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51726</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6009800000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8579600000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50397</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7492000000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07415</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07203</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.90376</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98178</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9353899999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17303</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15185</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86048</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15322</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60584</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.96848</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.0138</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15259</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.94829</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.98851</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58285</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92213</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.97946</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08704</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88352</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87115</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79167</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09435</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55141</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95794</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.9887899999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74212</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33128</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.49994</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.54376</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.57859</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49103</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.47228</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.48492</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83292</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7138300000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.7089500000000001</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.83228</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.56879</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.5502</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.60756</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.54887</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.5626599999999999</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45512</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6761900000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.50399</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46496</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56051</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.51932</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.51289</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.53972</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.50702</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.51318</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.51951</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5155599999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46983</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70087</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60273</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62778</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8491599999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27176</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16664</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8523500000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70151</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94041</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.1682</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12188</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01878</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54192</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44591</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56301</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.45534</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43318</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.49914</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.5732699999999999</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7023200000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.03934</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.10571</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97912</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98066</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56619</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54682</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94648</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08642</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78371</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01344</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76771</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64828</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64102</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70832</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80025</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29876</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.0632</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.65305</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.7858099999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.44646</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.27305</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62372</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65736</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67073</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.6658</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64277</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66727</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70019</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78199</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.6975</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70528</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71344</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63302</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74773</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02188</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13169</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69134</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.69978</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69355</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77318</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72334</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81274</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66625</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.05703</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.57314</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.48296</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3441</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.59309</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.16914</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47031</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49185</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.49919</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.48714</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7466799999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5105500000000001</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51877</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9219400000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47432</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17915</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90242</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76332</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43429</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7462799999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5149199999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.67962</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49579</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56623</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66444</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.51689</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.47702</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.68455</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.46532</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.43659</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51649</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54614</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76162</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76832</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47977</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54677</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50166</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72338</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7627699999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5543400000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5019100000000001</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02074</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48761</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44721</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09515</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13004</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08407</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11249</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12894</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01873</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19452</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14279</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13202</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17424</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84135</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19136</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84848</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34127</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73522</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94917</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.62689</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38466</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.53174</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5360499999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.52785</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7557999999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.33773</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.6039500000000001</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.5984700000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.5238200000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.50614</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.5821900000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5830599999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.57651</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.52574</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5660299999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50029</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49661</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.6339600000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.67588</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53399</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02139</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77164</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.73975</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27837</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.33992</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71604</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.63963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34638</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99405</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59028</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49256</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53855</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58899</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7320599999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17516</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91049</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6635599999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9321200000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.8787</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74343</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71268</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.1747</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17589</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42328</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23422</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61276</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20145</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28194</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07446</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39607</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03254</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.62906</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.1302</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6305700000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5317200000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80086</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6672899999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.6484</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50893</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.6648</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66317</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79545</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04649</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16522</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49941</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19179</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54595</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15286</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5566599999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.4973399999999999</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45903</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53796</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5150399999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5963999999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75601</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.1267</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6822</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.54622</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45698</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49247</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45434</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.57988</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47711</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44786</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44876</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.48678</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47594</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.4556</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36891</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.47678</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.6967899999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17045</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09544</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.68759</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55811</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49116</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80169</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48385</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09243</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36448</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.83521</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.79575</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52137</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75259</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75113</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.72239</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.56586</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7967799999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7524500000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52225</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.27831</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28167</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.2151</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.05938</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9517899999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28188</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54389</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49079</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.57477</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.74895</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54553</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54052</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21221</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75187</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75037</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.9833500000000001</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75849</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61758</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7495299999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17031</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72526</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23412</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8713200000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.85685</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.8784099999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15108</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63787</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.92948</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67771</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95441</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61672</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63479</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73397</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.6172</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.78929</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24226</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03319</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9935</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51192</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.33902</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04725</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75346</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34521</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5565800000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80075</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75222</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55877</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45834</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6267200000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5558500000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53696</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49417</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81128</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15179</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11811</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03102</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12083</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72388</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.71864</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04185</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06023</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66723</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55553</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54067</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65673</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54054</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04263</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65343</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54637</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49733</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57447</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55829</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51141</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42218</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4982</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5581199999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6567200000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15063</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.0536</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65799</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5796399999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.14976</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86298</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65723</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.13851</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81109</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50943</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49695</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53264</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34432</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.69745</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.57431</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.5808099999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7089299999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.54283</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6254400000000001</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58289</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6286499999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00268</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17177</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92353</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.95939</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.00846</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.94938</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91565</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.92948</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91274</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9150499999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6636299999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.01691</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6649700000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.01387</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.11696</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.09882</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6967100000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9198</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.84072</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.90761</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54115</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66495</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68742</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73583</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.7859</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.1958</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07591</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.0154</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32804</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01107</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11016</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91449</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75074</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.74999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8125800000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69065</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69072</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55547</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72338</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6838</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74593</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69392</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73182</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.9921599999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.88922</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00571</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.89358</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01352</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.99636</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.15527</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06571</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.08194</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5934299999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71653</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7037599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02585</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69608</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.7491</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13377</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.22295</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.42302</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.19191</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.35381</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9766699999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39176</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.37103</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.73457</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.64537</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.41287</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.41468</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80706</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7542300000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80148</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75361</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81114</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31381</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00418</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9342999999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96053</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03382</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.1625</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06151</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86453</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69353</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.2217</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20839</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15216</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86786</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70375</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09755</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10842</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10845</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13461</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10616</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5207200000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20146</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5771900000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73038</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.66264</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18547</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8612300000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06574</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.0308</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.04743</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03619</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06937</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12843</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05084</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06145</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18434</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16287</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21496</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20351</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26446</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16961</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14099</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12025</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10089</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12704</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17676</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19436</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17493</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07478</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6730700000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61383</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.56511</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54783</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44888</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.52996</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.3139</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31108</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06796</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47899</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51989</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43283</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84837</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5659500000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68289</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.69853</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75146</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94586</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15761</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30515</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44399</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43217</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45968</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54437</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25143</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85126</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61527</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73327</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006599999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50292</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84438</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.86556</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21307</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77311</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5803400000000001</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62624</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70651</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58196</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7343099999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60927</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19899</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17573</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41094</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17706</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17811</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18328</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10235</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07712</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20748</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10485</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19117</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.04963</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08127</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20656</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08103</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.5418</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80724</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80413</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56404</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21261</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84914</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84964</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55913</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5545800000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5625399999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51549</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539500000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5212100000000001</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45974</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45998</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49521</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992200000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5478099999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5576100000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17569</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8830399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49402</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.16955</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5095</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694199999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84417</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79516</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8529500000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50076</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52299</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17774</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70102</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17341</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5492899999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55044</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5808099999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79965</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55514</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7992400000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8491299999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7987300000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835800000000001</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05009</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17577</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17703</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17496</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8242999999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73237</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6762899999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6842699999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73102</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8349099999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81811</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80629</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75602</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13635</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7499600000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60949</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63562</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6170800000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61449</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7029099999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67025</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7041000000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60815</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53101</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
